--- a/pacjenci/KURZEJA ROMAN.xlsx
+++ b/pacjenci/KURZEJA ROMAN.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/KURZEJA ROMAN.xlsx
+++ b/pacjenci/KURZEJA ROMAN.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -452,372 +452,269 @@
           <t>SUVmax</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>07.09.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Agresywny chłoniak B komórkowy. Ocena zaawansowania przed rozpoczęciem leczenia.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 122mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie obszar w szczęce w topografii zęba 17 po stronie prawej - do konsultacji stomatologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pogrubienie błony śluzowej obu zatok szczękowych, większe po stronie prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego.  Brzuch i miednica: Aktywny metabolicznie naciek obejmujący wpust i dno żołądka wielkości wg PET 77x58x38mm, SUV max 16,9. Mierne pobudzenie metaboliczne w topografii mas miękkotkankowych pomiędzy aortą a głową trzustki oraz pomiędzy VCI i żyłą wrotną średnicy wg PET do 24mm, SUV max 4,0 - w pierwszej kolejności  pakiety węzłowe. Nieco niejednorodny metabolizm FDG w wątrobie.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wartości referencyjne: MBPS SUVmax 2,2, Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie naciek w topografii wpust i dno żołądka oraz  pobudzenie metaboliczne w topografii mas miękkotkankowych pomiędzy aorta a głową trzustki oraz pomiędzy VCI i żyłą wrotną  - pakiety węzłowe.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>16.9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>12.12.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Agresywny chłoniak B komórkowy. Ocena po 3 cyklach chemioterapii RCHOP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 121mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie obszar w szczęce w topografii zęba 47 po stronie prawej, SUV max 5,3 - do konsultacji stomatologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pogrubienie błony śluzowej obu zatok szczękowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Zagęszczenia miąższowe w segmencie 10 płuca prawego - do oceny klinicznej.   Brzuch i miednica: Mierna, rozlana aktywność metaboliczna w topografii dna żołądka oraz trzonu, SUV max do 3,8.  Nieco niejednorodny metabolizm FDG w wątrobie.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne masy miękkotkankowe pomiędzy aorta a głową trzustki oraz pomiędzy VCI i żyłą wrotną średnicy do 11mm.   Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,0, Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>16.02.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy agresywny żołądka DLBCL-NOS. Po 6 cyklu RCHOP (01.02.2023).</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 131 mg%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Symetrycznie wzmożony metabolizm FDG w obu fałdach głosowych SUV max 6,7-czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Wydatne zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy prawej zatoki czołowej. Masywne zgrubienia błony śluzowej w prawej zatoce szczękowej. Przyścienne i polipowate zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce klinowej. Wskazana kontrola laryngologiczna.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar u podstawy segmentu 3 płuca prawego w topografii guzkowych zagęszczeń miąższowych, na obszarze wielkości ok. 24x23x19 mm, SUV max 6,8 [Im fuz. 120]. Pobudzona metabolicznie zmiana guzkowa w segmencie 4/5 płuca prawego wielkości 8x5 mm SUV max 3,2 [Im fuz.145]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 4mm obwodowy guzek w segm. 4 płuca prawego. Dość liczne drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku  SUV max do 4,3.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne pomiędzy aortą a głową trzustki oraz pomiędzy VCI i żyłą wrotną średnicy do 10mm. Mierne pogrubienie trzonu nadnercza lewego.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie zmian w segmencie 3 płuca prawego oraz pobudzonego metabolicznie guzka w płacie środkowym płuca prawego - do oceny z całością obrazu klinicznego i weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>6.8</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>30.05.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy agresywny żołądka DLBCL-NOS. Ostatnia chemioterapia II 2023.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 122mg%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Wydatne zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy prawej zatoki czołowej. Masywne zgrubienia błony śluzowej w prawej zatoce szczękowej. Przyścienne i polipowate zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce klinowej.   Klatka piersiowa i śródpiersie: Obszar zmian włóknisto-guzkowych u podstawy segmentu 3 płuca prawego wielkości ok. 28x20 mm - obecnie dochodzący do opłucnej, SUV max do 3,6 [Im fuz. 122]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 4mm obwodowy guzek w segm. 4 płuca prawego. Dość liczne drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonego metabolicznie obszaru w topografii płuca prawego - do dalszej kontroli - w porówaniu z badaniem z 02.2023 regresja metaboliczna, zmiana mofologii w przeglądowym badaniu TK - celowa kontrola - ewolucja zmian zapalnych ? nacieku w przebiegu ch. podstawowej? Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>27.11.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>DLBCL. Ostatnia ChTh w 02.2023.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 131 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Zgrubienia błony śluzowej w sitowiu obustronnie. Zgrubienia błony śluzowej w prawej zatoce szczękowej. Przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce klinowej. Wskazana kontrola laryngologiczna.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 4x2mm guzek w szczycie płuca lewego. Ok. 4mm obwodowy guzek w segm. 4 płuca prawego. Ok. 5mm uwapniony obwodowy guzek w segm. 3/5 płuca lewego. Ok. 6mm guzek w segm. 3/4 płuca prawego. Drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 3,5- czynnościowo?.  Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Dość liczne drobne i miernie powiększone węzły chłonne pachwinowe i udowe obustronnie, wielkości do 23x13mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej  metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>30.04.2024</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>DLBCL. Stan po ChTh  zakończonej 02.2023. Ocena remisji.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 151 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Zgrubienia błony śluzowej w sitowiu obustronnie. Przyścienne i polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej wielkości 8x4 mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Obszar mlecznej szyby, wyraźnie ograniczony, przyśródpiersiowo w płacie górnym płuca prawego, wielkości 28x16mm - do wcześniejszej kontroli. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 5x3mm guzek w szczycie płuca lewego. Niewielki, nieostro ograniczony obszar mlecznej szyby przyśródpiersiowo w płacie górnym płuca lewego. Niewielkie pasmowate zmiany włókniste u podstawy płata górnego prawego płuca. Ok. 4,5mm obwodowy guzek w segm. 4 płuca prawego. Ok. 5mm uwapniony obwodowy guzek w segm. 3/5 płuca lewego. Ok. 6mm guzek w segm. 3/4 płuca prawego. Drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny pachwinowy prawy wielkości 12x9 mm, SUV max 4,1 [Im fuz. 267] Pobudzony metabolicznie węzeł chłonny udowy lewy wielkości 14x19 mm, SUV max 2,4 [Im fuz. 285] Odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 3,5-  w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w wątrobie, z cechami nasilonej steatosis. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Drobne węzły chłonne przyaortalne, zwłaszcza lewe. Poza powyższymi dość liczne drobne i pojedyncze wydatniejsze węzły chłonne pachwinowe i udowe obustronnie.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Spondylolisteza przednia na poziomie L4/L5 o ok. 4mm. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Drobne odczyny okostnowe [zwłaszcza po prawej] oraz wydatna osteofitoza dystalnych części talerzy obu kości biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych, wydatniejsze po stronie prawej, z ok. 16mm ubytkiem osteolitycznym w panewce.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego pachwinowego prawego- wznowa choroby? odczynowy? Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>4.1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>25.03.2025</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>DLBCL. Stan po Ch-Th  zakończonej 02.2023. Ocena remisji.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 130 mg%.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyjne po stronie prawej: - grupy 1B wielkości 15x11 mm SUV max 3,3; - grupy 3 średnicy 8 mm SUV max 3,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Zgrubienia błony śluzowej w sitowiu obustronnie. Przyścienne i polipowate zgrubienia błony śluzowej w obu zatokach szczękowych, większe w prawej. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej wielkości 8x14 mm - wskazana kontrola laryngologiczna.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe prawe z widocznymi zatokami tłuszczowymi wielkości do 14x10 mm SUV max do 2,6 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Obszar mlecznej szyby, wyraźnie ograniczony, przyśródpiersiowo w płacie górnym płuca prawego, wielkości 28x16mm - jak poprzednio. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 8mm guzek w segm. 3/4 płuca prawego. Ok. 5x3mm guzek w szczycie płuca lewego. Niewielki, nieostro ograniczony obszar mlecznej szyby przyśródpiersiowo w płacie górnym płuca lewego. Niewielkie pasmowate zmiany włókniste u podstawy płata górnego prawego płuca. Ok. 4,5mm obwodowy guzek w segm. 4 płuca prawego. Ok. 5mm uwapniony obwodowy guzek w segm. 3/5 płuca lewego. Drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Nieaktywne metabolicznie węzły chłonne pachowe lewe wielkości do 13x9mm (SUV max do 2,2).  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych, wielkości do 12x18 mm SUV max do 5,4 - pachwinowy prawy wielkości 19x15 mm, SUV max 8,7   Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 4,8-  w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w wątrobie, z cechami nasilonej steatosis. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Drobne węzły chłonne przyaortalne, zwłaszcza lewe. Poza powyższymi dość liczne drobne i pojedyncze wydatniejsze węzły chłonne pachwinowe i udowe obustronnie, wielkości do 18x11mm (SUV max do 2,1). Miernie powiększona prostata. Pęcherz moczowy o pogrubiałych ścianach.  Układ kostny: Odcinkowo pobudzenie metaboliczne w zmianach zwyrodnieniowych kręgosłupa, głównie w odcinku lędźwiowym. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Spondylolisteza przednia na poziomie L4/L5 o ok. 4mm. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Drobne odczyny okostnowe [zwłaszcza po prawej] oraz wydatna osteofitoza dystalnych części talerzy obu kości biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych, wydatniejsze po stronie prawej, z ok. 16mm ubytkiem osteolitycznym w panewce.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych w miednicy oraz pojedynczych w obrębie szyi po stronie prawej - w pierwszej kolejności wznowa procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>13.11.2025</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>DLBCL. Stan po Ch-Th  zakończonej 02.2023. Ocena remisji - PET niejednoznaczny, weryfikacja hist-pat węzła chłonnego z pachwiny negatywna.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 130 mg%.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyjne po stronie prawej: - grupy 2B wielkości 16x13 mm SUV max 4,2; - grupy 3 średnicy do 9 mm SUV max do 3,6; - grupy 5B średnicy 9 mm SUV max 2,9. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Zgrubienia błony śluzowej w sitowiu obustronnie. Przyścienne i polipowate zgrubienia błony śluzowej w obu zatokach szczękowych, większe w prawej. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej wielkości 9x15 mm - wskazana kontrola laryngologiczna.  Klatka piersiowa i śródpiersie: Miernie aktywne metabolicznie węzły chłonne pachowe prawe wielkości do 19x14 mm SUV max do 3,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w segmencie 1/2 płuca prawego. Ok. 8mm guzek w segm. 3/4 płuca prawego. Ok. 6x4mm zmiana guzkowo-włóknista w szczycie płuca lewego. Niewielki, nieostro ograniczony obszar mlecznej szyby przyśródpiersiowo w płacie górnym płuca lewego. Niewielkie pasmowate zmiany włókniste u podstawy płata górnego prawego płuca. Ok. 4,5mm obwodowy guzek w segm. 4 płuca prawego. Ok. 5mm uwapniony obwodowy guzek w segm. 3/5 płuca lewego. Drobne zmiany guzkowe i guzkowo-włókniste w segm. 5 i 4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Nieaktywne metabolicznie węzły chłonne pachowe lewe wielkości do 13x9mm (SUV max do 1,6).  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych, wielkości do 17x36 mm SUV max do 8,5, - pachwinowy prawy wielkości 20x39 mm, SUV max 19,5, - pachwinowy lewy średnicy 11 mm, SUV max 4,3.  Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 12,1 -  w pierwszej kolejności o charakterze czynnościowym. Niejednorodny metabolizm FDG w wątrobie, z cechami nasilonej steatosis. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Drobne węzły chłonne przyaortalne, zwłaszcza lewe. Miernie powiększona prostata. Pęcherz moczowy o pogrubiałych ścianach.  Układ kostny: Odcinkowo pobudzenie metaboliczne w topografii zmian zwyrodnieniowych kręgosłupa, głównie w odcinku lędźwiowym. Cechy uogólnionego zaniku kostnego. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym [ciasne na poziomie C5/C6 i C6/C7], piersiowym i lędźwiowym kręgosłupa. Wydatniejszy osteofit/drobny odłam kostny widoczny jest w przyleganiu do przedniego obrysu przestrzeni międzykręgowej na poziomie Th10/Th11. Spondylolisteza przednia na poziomie L4/L5 o ok. 4mm. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [wydatne w odcinku lędźwiowym] i w stawach żebrowo-poprzecznych. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych. Drobne odczyny okostnowe [zwłaszcza po prawej] oraz wydatna osteofitoza dystalnych części talerzy obu kości biodrowych. Zmiany zwyrodnieniowe w stawach biodrowych, wydatniejsze po stronie prawej, z ok. 16mm ubytkiem osteolitycznym w panewce.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych w miednicy oraz pojedynczych w obrębie szyi po stronie prawej. W porównaniu do badania poprzedniego z 27.11.2023 progresja wielkości i aktywność metabolicznej niektórych ze zmian. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>19.5</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
       </c>
     </row>
   </sheetData>
